--- a/output/supplementary/P1_stratified_by_Pathway.xlsx
+++ b/output/supplementary/P1_stratified_by_Pathway.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,85 +565,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4407096171802054</v>
+        <v>0.4408201304753029</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2829131652661064</v>
+        <v>0.282385834109972</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2474323062558357</v>
+        <v>0.2469711090400745</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2225212939714329</v>
+        <v>0.2221001528683275</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2741487269879345</v>
+        <v>0.2736474111187994</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2082166199813259</v>
+        <v>0.2078285181733458</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1849629051306801</v>
+        <v>0.1846134659104004</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2335560654785706</v>
+        <v>0.2331281963730776</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05695611577964519</v>
+        <v>0.05684995340167754</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04459398174314987</v>
+        <v>0.04451038746905927</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0724852232299364</v>
+        <v>0.07235136824320149</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2334267040149393</v>
+        <v>0.2329916123019571</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2090722746719672</v>
+        <v>0.2086768363749706</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2596866568766443</v>
+        <v>0.2592114770037102</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2735760971055089</v>
+        <v>0.2730661696178938</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2477218027256642</v>
+        <v>0.2472524156024376</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3010489184671146</v>
+        <v>0.3004990828537886</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1017740429505135</v>
+        <v>0.1015843429636533</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08506569471126506</v>
+        <v>0.08490581118175809</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1213289963762403</v>
+        <v>0.12110554647753</v>
       </c>
       <c r="W2" t="n">
-        <v>0.08309990662931839</v>
+        <v>0.08294501397949673</v>
       </c>
       <c r="X2" t="n">
-        <v>0.06802049454484277</v>
+        <v>0.06789278057191071</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1011594106616547</v>
+        <v>0.1009729096094493</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1064425770308123</v>
+        <v>0.1071761416589003</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0893580846394936</v>
+        <v>0.09004828182025029</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1263403029182638</v>
+        <v>0.1271067760824162</v>
       </c>
     </row>
     <row r="3">
@@ -653,119 +653,119 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.375</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.375</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1582169222626268</v>
+        <v>0.1368417594615211</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7495457695909742</v>
+        <v>0.6942621454161981</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02567895594897479</v>
+        <v>0.02241690886329617</v>
       </c>
       <c r="J3" t="n">
-        <v>0.51313450331903</v>
+        <v>0.4708948057698615</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02567895594897479</v>
+        <v>0.02241690886329617</v>
       </c>
       <c r="M3" t="n">
-        <v>0.51313450331903</v>
+        <v>0.4708948057698615</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08221716570901549</v>
+        <v>0.07147768885802763</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6410709098517873</v>
+        <v>0.5907301208974108</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02567895594897479</v>
+        <v>0.02241690886329617</v>
       </c>
       <c r="S3" t="n">
-        <v>0.51313450331903</v>
+        <v>0.4708948057698615</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08221716570901549</v>
+        <v>0.07147768885802763</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6410709098517873</v>
+        <v>0.5907301208974108</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="X3" t="n">
-        <v>0.08221716570901549</v>
+        <v>0.07147768885802763</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6410709098517873</v>
+        <v>0.5907301208974108</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2504542304090258</v>
+        <v>0.2152125268244419</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8417830777373732</v>
+        <v>0.7847874731755582</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>PMA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.07147768885802763</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5615060804490177</v>
+        <v>0.5907301208974108</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.07147768885802763</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5615060804490177</v>
+        <v>0.5907301208974108</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -774,25 +774,25 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5615060804490177</v>
+        <v>0.3244156195108769</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.07147768885802763</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5615060804490177</v>
+        <v>0.5907301208974108</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.07147768885802763</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5615060804490177</v>
+        <v>0.5907301208974108</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5615060804490177</v>
+        <v>0.3244156195108769</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -810,103 +810,15 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5615060804490177</v>
+        <v>0.3244156195108769</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0614903152761605</v>
+        <v>0.2152125268244419</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7923450448735121</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PMA</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.07147768885802763</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.5907301208974108</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.07147768885802763</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5907301208974108</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.3244156195108769</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.07147768885802763</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.5907301208974108</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.07147768885802763</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.5907301208974108</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.3244156195108769</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.3244156195108769</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.2152125268244419</v>
-      </c>
-      <c r="AB5" t="n">
         <v>0.7847874731755582</v>
       </c>
     </row>
